--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_67595_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_67595_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R04702b5977844ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdb1327c7ed804bf6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4705</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.7953</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.7953</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.8162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.2948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_67595_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_67595_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdb1327c7ed804bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd35dd10f15db47ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.5655</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9549</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.0820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.2948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3489</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.8923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.0296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.3786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.9549</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.0820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.8480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.2948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.5655</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6128</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.2948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.7774</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.6182</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     17.2948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
